--- a/data/trans_orig/P37-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2007</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>246929</t>
+          <t>248290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>302932</t>
+          <t>305099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>356441</t>
+          <t>356895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>423980</t>
+          <t>422080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>623242</t>
+          <t>621604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>709817</t>
+          <t>706206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>728791</t>
+          <t>726624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>784794</t>
+          <t>783433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>891133</t>
+          <t>893033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>958672</t>
+          <t>958218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1637018</t>
+          <t>1640629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1723593</t>
+          <t>1725231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>97422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142403</t>
+          <t>141309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80557</t>
+          <t>80187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121769</t>
+          <t>120988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190074</t>
+          <t>189468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>247422</t>
+          <t>246013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1550095</t>
+          <t>1551189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1593397</t>
+          <t>1595076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1464007</t>
+          <t>1464788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1505219</t>
+          <t>1505589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3030852</t>
+          <t>3032261</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3088200</t>
+          <t>3088806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48200</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78484</t>
+          <t>79370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32892</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>58386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89230</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130873</t>
+          <t>130106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472074</t>
+          <t>471188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>502358</t>
+          <t>503047</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416912</t>
+          <t>418026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443520</t>
+          <t>443020</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896096</t>
+          <t>896863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937739</t>
+          <t>937788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>415220</t>
+          <t>417913</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>490166</t>
+          <t>490096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>491392</t>
+          <t>494083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>576847</t>
+          <t>574991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>936157</t>
+          <t>933527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1051755</t>
+          <t>1045896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2784613</t>
+          <t>2784683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2859559</t>
+          <t>2856866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2800453</t>
+          <t>2802309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2885908</t>
+          <t>2883217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5600324</t>
+          <t>5606183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5715922</t>
+          <t>5718552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2012</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>309030</t>
+          <t>315295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>371751</t>
+          <t>378285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>413583</t>
+          <t>414286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>486670</t>
+          <t>485067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>743416</t>
+          <t>744513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>834106</t>
+          <t>841965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>601865</t>
+          <t>595331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664586</t>
+          <t>658321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>851127</t>
+          <t>852730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>924214</t>
+          <t>923511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1477306</t>
+          <t>1469447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1567996</t>
+          <t>1566899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183140</t>
+          <t>181174</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241298</t>
+          <t>239456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132142</t>
+          <t>132649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184696</t>
+          <t>184477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>330244</t>
+          <t>330078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>406482</t>
+          <t>404835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1719677</t>
+          <t>1721519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1777835</t>
+          <t>1779801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1572036</t>
+          <t>1572255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1624590</t>
+          <t>1624083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3311225</t>
+          <t>3312872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3387463</t>
+          <t>3387629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39893</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71512</t>
+          <t>68174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>30189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56808</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75602</t>
+          <t>74627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116689</t>
+          <t>118121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>408655</t>
+          <t>411993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440274</t>
+          <t>441761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401823</t>
+          <t>400670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>428260</t>
+          <t>428442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822109</t>
+          <t>820677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>863196</t>
+          <t>864171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>559132</t>
+          <t>560136</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>653680</t>
+          <t>649726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>604630</t>
+          <t>602752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>701873</t>
+          <t>696557</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1185392</t>
+          <t>1187017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1319694</t>
+          <t>1320952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2761078</t>
+          <t>2765032</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2855626</t>
+          <t>2854622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2851286</t>
+          <t>2856602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2948529</t>
+          <t>2950407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5648223</t>
+          <t>5646965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5782525</t>
+          <t>5780900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2016</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>232451</t>
+          <t>232316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>281921</t>
+          <t>282363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>319968</t>
+          <t>324798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>386981</t>
+          <t>385997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>567974</t>
+          <t>567499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>652224</t>
+          <t>651165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>472426</t>
+          <t>471984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>521896</t>
+          <t>522031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>607679</t>
+          <t>608663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>674692</t>
+          <t>669862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1096783</t>
+          <t>1097842</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1181033</t>
+          <t>1181508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188290</t>
+          <t>189323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244034</t>
+          <t>245463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173240</t>
+          <t>176164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233231</t>
+          <t>236099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377434</t>
+          <t>377890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>457440</t>
+          <t>456032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1832351</t>
+          <t>1830922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1888095</t>
+          <t>1887062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1755069</t>
+          <t>1752201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1815060</t>
+          <t>1812136</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3607245</t>
+          <t>3608653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3687251</t>
+          <t>3686795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76987</t>
+          <t>75268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42778</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72251</t>
+          <t>71556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96354</t>
+          <t>94522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140036</t>
+          <t>137758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469899</t>
+          <t>471618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500491</t>
+          <t>503255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>476889</t>
+          <t>477584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>506362</t>
+          <t>507274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>955991</t>
+          <t>958269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999673</t>
+          <t>1001505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>487594</t>
+          <t>490665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>575651</t>
+          <t>570476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>564447</t>
+          <t>563781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>655983</t>
+          <t>660200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1075348</t>
+          <t>1076388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1205669</t>
+          <t>1203837</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2801967</t>
+          <t>2807142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2890024</t>
+          <t>2886953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2876117</t>
+          <t>2871900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2967653</t>
+          <t>2968319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5704049</t>
+          <t>5705881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5834370</t>
+          <t>5833330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2023</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259760</t>
+          <t>259606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>301967</t>
+          <t>304226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>466434</t>
+          <t>464662</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>507548</t>
+          <t>508203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>739509</t>
+          <t>738271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>799327</t>
+          <t>800948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212971</t>
+          <t>210712</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255178</t>
+          <t>255332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245620</t>
+          <t>244965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286734</t>
+          <t>288506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>468780</t>
+          <t>467159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528598</t>
+          <t>529836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>349645</t>
+          <t>348641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>577249</t>
+          <t>576670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>561342</t>
+          <t>562251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1130854</t>
+          <t>1103221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1031853</t>
+          <t>1024464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1723127</t>
+          <t>1735781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1713078</t>
+          <t>1713657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1940682</t>
+          <t>1941686</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1106969</t>
+          <t>1134602</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1676481</t>
+          <t>1675572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2805023</t>
+          <t>2792369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3496297</t>
+          <t>3503686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,38%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189203</t>
+          <t>191326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240572</t>
+          <t>241420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185075</t>
+          <t>185062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225096</t>
+          <t>225990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>387021</t>
+          <t>390940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>454630</t>
+          <t>452380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406051</t>
+          <t>405203</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457420</t>
+          <t>455297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435367</t>
+          <t>434473</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475388</t>
+          <t>475401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>852456</t>
+          <t>854706</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>920065</t>
+          <t>916146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>772265</t>
+          <t>765679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1098645</t>
+          <t>1092943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1265437</t>
+          <t>1268417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1832578</t>
+          <t>1861979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2172940</t>
+          <t>2171809</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2887364</t>
+          <t>2896188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2353244</t>
+          <t>2358946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2679624</t>
+          <t>2686210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1818877</t>
+          <t>1789476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2386018</t>
+          <t>2383038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4215980</t>
+          <t>4207156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4930404</t>
+          <t>4931535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248290</t>
+          <t>249696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>305099</t>
+          <t>305252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>356895</t>
+          <t>357355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>422080</t>
+          <t>424126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>621604</t>
+          <t>624059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>706206</t>
+          <t>710917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726624</t>
+          <t>726471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>783433</t>
+          <t>782027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>893033</t>
+          <t>890987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>958218</t>
+          <t>957758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1640629</t>
+          <t>1635918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1725231</t>
+          <t>1722776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97422</t>
+          <t>97178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141309</t>
+          <t>141906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80187</t>
+          <t>82089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120988</t>
+          <t>120265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189468</t>
+          <t>187110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246013</t>
+          <t>246986</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1551189</t>
+          <t>1550592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1595076</t>
+          <t>1595320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1464788</t>
+          <t>1465511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1505589</t>
+          <t>1503687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3032261</t>
+          <t>3031288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3088806</t>
+          <t>3091164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47511</t>
+          <t>47270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>78177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>58938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89181</t>
+          <t>88466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130106</t>
+          <t>128900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471188</t>
+          <t>472381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503047</t>
+          <t>503288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>418026</t>
+          <t>417474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443020</t>
+          <t>442552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896863</t>
+          <t>898069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937788</t>
+          <t>938503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>417913</t>
+          <t>416507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>490096</t>
+          <t>494851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>494083</t>
+          <t>490061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>574991</t>
+          <t>578056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>933527</t>
+          <t>932541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1045896</t>
+          <t>1048028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2784683</t>
+          <t>2779928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2856866</t>
+          <t>2858272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2802309</t>
+          <t>2799244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2883217</t>
+          <t>2887239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5606183</t>
+          <t>5604051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5718552</t>
+          <t>5719538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>315295</t>
+          <t>311206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>378285</t>
+          <t>369256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>414286</t>
+          <t>414964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>485067</t>
+          <t>485253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>744513</t>
+          <t>745711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>841965</t>
+          <t>839029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>595331</t>
+          <t>604360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>658321</t>
+          <t>662410</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>852730</t>
+          <t>852544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>923511</t>
+          <t>922833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1469447</t>
+          <t>1472383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1566899</t>
+          <t>1565701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181174</t>
+          <t>181408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239456</t>
+          <t>237231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132649</t>
+          <t>133944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184477</t>
+          <t>183954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>330078</t>
+          <t>326735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404835</t>
+          <t>405608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1721519</t>
+          <t>1723744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1779801</t>
+          <t>1779567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1572255</t>
+          <t>1572778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1624083</t>
+          <t>1622788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3312872</t>
+          <t>3312099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3387629</t>
+          <t>3390972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68174</t>
+          <t>70038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57961</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74627</t>
+          <t>74861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118121</t>
+          <t>113945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>411993</t>
+          <t>410129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>441761</t>
+          <t>440783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>400670</t>
+          <t>401895</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>428442</t>
+          <t>430009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>820677</t>
+          <t>824853</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>864171</t>
+          <t>863937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>560136</t>
+          <t>559477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>649726</t>
+          <t>656442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>602752</t>
+          <t>602926</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>696557</t>
+          <t>698836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1187017</t>
+          <t>1184716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1320952</t>
+          <t>1316580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2765032</t>
+          <t>2758316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2854622</t>
+          <t>2855281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2856602</t>
+          <t>2854323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2950407</t>
+          <t>2950233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5646965</t>
+          <t>5651337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5780900</t>
+          <t>5783201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>232316</t>
+          <t>231829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282363</t>
+          <t>280752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>324798</t>
+          <t>320591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>385997</t>
+          <t>385822</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>567499</t>
+          <t>568726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>651165</t>
+          <t>651676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471984</t>
+          <t>473595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>522031</t>
+          <t>522518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>608663</t>
+          <t>608838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669862</t>
+          <t>674069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1097842</t>
+          <t>1097331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1181508</t>
+          <t>1180281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189323</t>
+          <t>189946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245463</t>
+          <t>246904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176164</t>
+          <t>173041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>236099</t>
+          <t>232489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377890</t>
+          <t>381004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>456032</t>
+          <t>459846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1830922</t>
+          <t>1829481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1887062</t>
+          <t>1886439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1752201</t>
+          <t>1755811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1812136</t>
+          <t>1815259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3608653</t>
+          <t>3604839</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3686795</t>
+          <t>3683681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75268</t>
+          <t>74448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41866</t>
+          <t>42698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71556</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94522</t>
+          <t>94887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>137758</t>
+          <t>138338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471618</t>
+          <t>472438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503255</t>
+          <t>502235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>477584</t>
+          <t>476264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507274</t>
+          <t>506442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>958269</t>
+          <t>957689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1001505</t>
+          <t>1001140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>490665</t>
+          <t>487887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>570476</t>
+          <t>575024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>563781</t>
+          <t>566482</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>660200</t>
+          <t>661705</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1076388</t>
+          <t>1072875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1203837</t>
+          <t>1205437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2807142</t>
+          <t>2802594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2886953</t>
+          <t>2889731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2871900</t>
+          <t>2870395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2968319</t>
+          <t>2965618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5705881</t>
+          <t>5704281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5833330</t>
+          <t>5836843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300817</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259606</t>
+          <t>278574</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304226</t>
+          <t>325379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>488370</t>
+          <t>530239</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>464662</t>
+          <t>508004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>508203</t>
+          <t>551935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>769562</t>
+          <t>831057</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>738271</t>
+          <t>797625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>800948</t>
+          <t>866323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>233747</t>
+          <t>277712</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210712</t>
+          <t>253150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255332</t>
+          <t>299955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>264798</t>
+          <t>291076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244965</t>
+          <t>269380</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288506</t>
+          <t>313311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>498545</t>
+          <t>568788</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>467159</t>
+          <t>533522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529836</t>
+          <t>602220</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504076</t>
+          <t>553150</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>348641</t>
+          <t>512117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>576670</t>
+          <t>598381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>732865</t>
+          <t>582396</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>562251</t>
+          <t>545310</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1103221</t>
+          <t>616559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1236941</t>
+          <t>1135546</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1024464</t>
+          <t>1082941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1735781</t>
+          <t>1195995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1786251</t>
+          <t>1677416</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1713657</t>
+          <t>1632185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1941686</t>
+          <t>1718449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1504958</t>
+          <t>1588996</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1134602</t>
+          <t>1554833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1675572</t>
+          <t>1626082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3291209</t>
+          <t>3266413</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2792369</t>
+          <t>3205964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3503686</t>
+          <t>3319018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>215525</t>
+          <t>233900</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191326</t>
+          <t>208799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241420</t>
+          <t>260222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>204094</t>
+          <t>227893</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185062</t>
+          <t>206484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225990</t>
+          <t>249642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>419620</t>
+          <t>461793</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390940</t>
+          <t>429469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>452380</t>
+          <t>494300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>431098</t>
+          <t>477687</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405203</t>
+          <t>451365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455297</t>
+          <t>502788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>456369</t>
+          <t>506984</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434473</t>
+          <t>485235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475401</t>
+          <t>528393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>887466</t>
+          <t>984671</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854706</t>
+          <t>952164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>916146</t>
+          <t>1016995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1000793</t>
+          <t>1087867</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>765679</t>
+          <t>1031834</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1092943</t>
+          <t>1146053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1425330</t>
+          <t>1340529</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1268417</t>
+          <t>1291981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1861979</t>
+          <t>1391189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2426123</t>
+          <t>2428396</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2171809</t>
+          <t>2351770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2896188</t>
+          <t>2506792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2451096</t>
+          <t>2432816</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2358946</t>
+          <t>2374630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2686210</t>
+          <t>2488849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2226125</t>
+          <t>2387056</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1789476</t>
+          <t>2336396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2383038</t>
+          <t>2435604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4677221</t>
+          <t>4819871</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4207156</t>
+          <t>4741475</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4931535</t>
+          <t>4896497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7103344</t>
+          <t>7248267</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7103344</t>
+          <t>7248267</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7103344</t>
+          <t>7248267</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
